--- a/Digital Wallet — Deposit & Transaction QA/Digital_Wallet_Risk_Matrix_Final.xlsx
+++ b/Digital Wallet — Deposit & Transaction QA/Digital_Wallet_Risk_Matrix_Final.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000"/>
+    <workbookView windowWidth="22188" windowHeight="9000" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Risk Matrix" sheetId="1" r:id="rId1"/>
@@ -201,61 +201,61 @@
     <t>Purpose</t>
   </si>
   <si>
-    <t>Prioritize functional risks identified from the requirements and the 20 executed test cases in the Digital Wallet mini project.</t>
+    <t>Priorizar los riesgos funcionales identificados a partir de los requisitos y los 20 casos de prueba ejecutados en el miniproyecto Digital Wallet.</t>
   </si>
   <si>
     <t>Impact - HIGH</t>
   </si>
   <si>
-    <t>Potential effect on critical wallet behavior such as balance accuracy, transaction integrity, or financial data.</t>
+    <t>Posible impacto en el funcionamiento crítico de la billetera digital, como la precisión del saldo, la integridad de las transacciones o los datos financieros.</t>
   </si>
   <si>
     <t>Impact - MEDIUM</t>
   </si>
   <si>
-    <t>Important functional or usability effect without the same direct impact on balance integrity.</t>
+    <t>Impacto funcional o de usabilidad importante, sin afectar directamente la integridad del saldo en la misma medida.</t>
   </si>
   <si>
     <t>Impact - LOW</t>
   </si>
   <si>
-    <t>Limited consequence if the risk occurs.</t>
+    <t>Consecuencia limitada si el riesgo llega a materializarse.</t>
   </si>
   <si>
     <t>Likelihood - HIGH</t>
   </si>
   <si>
-    <t>Qualitative assessment that the risk is likely to occur under normal or common conditions.</t>
+    <t>Evaluación cualitativa que indica que es probable que el riesgo ocurra en condiciones normales o habituales.</t>
   </si>
   <si>
     <t>Likelihood - MEDIUM</t>
   </si>
   <si>
-    <t>Qualitative assessment that the risk can occur under certain conditions.</t>
+    <t>Evaluación cualitativa que indica que el riesgo puede ocurrir bajo determinadas condiciones.</t>
   </si>
   <si>
     <t>Likelihood - LOW</t>
   </si>
   <si>
-    <t>Qualitative assessment that the risk is less likely or requires specific conditions.</t>
+    <t>Evaluación cualitativa que indica que es menos probable que el riesgo ocurra o que requiere condiciones específicas</t>
   </si>
   <si>
     <t>Risk Level</t>
   </si>
   <si>
-    <t>Qualitative result derived from Impact and Likelihood using the matrix below.</t>
+    <t>Resultado cualitativo obtenido a partir del impacto y la probabilidad de ocurrencia, utilizando la matriz que aparece a continuación.</t>
   </si>
   <si>
     <t>Matrix</t>
   </si>
   <si>
-    <t>LOW impact + LOW likelihood = LOW; LOW + MEDIUM = LOW; LOW + HIGH = MEDIUM; MEDIUM + LOW = LOW; MEDIUM + MEDIUM = MEDIUM; MEDIUM + HIGH = HIGH; HIGH + LOW = MEDIUM; HIGH + MEDIUM = HIGH; HIGH + HIGH = HIGH.</t>
+    <t>Impacto BAJO + probabilidad BAJA = riesgo BAJO; BAJO + MEDIA = BAJO; BAJO + ALTA = MEDIO; MEDIO + BAJA = BAJO; MEDIO + MEDIA = MEDIO; MEDIO + ALTA = ALTO; ALTO + BAJA = MEDIO; ALTO + MEDIA = ALTO; ALTO + ALTA = ALTO.</t>
   </si>
   <si>
     <t>Important</t>
   </si>
   <si>
-    <t>Likelihood is a qualitative QA assessment for this portfolio project, not a statistical probability. PASS results indicate expected behavior was observed during execution; they do not eliminate the underlying risk.</t>
+    <t>La probabilidad de ocurrencia es una evaluación cualitativa de QA para este proyecto de portafolio, no una probabilidad estadística. Los resultados PASS (APROBADO) indican que durante la ejecución se observó el comportamiento esperado, pero no eliminan el riesgo subyacente.</t>
   </si>
 </sst>
 </file>
@@ -268,7 +268,7 @@
     <numFmt numFmtId="176" formatCode="_-\$* #,##0.00_-;\-\$* #,##0.00_-;_-\$* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-\$* #,##0_-;\-\$* #,##0_-;_-\$* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,13 +279,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -777,148 +770,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1553,7 +1546,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" ht="28.8" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>57</v>
       </c>
@@ -1617,7 +1610,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:2">
+    <row r="10" ht="43.2" spans="1:2">
       <c r="A10" s="1" t="s">
         <v>73</v>
       </c>
